--- a/data/la_villa_letira_becara.xlsx
+++ b/data/la_villa_letira_becara.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,30 +462,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -510,24 +525,33 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>19</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>27</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>20</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>16</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -550,24 +574,33 @@
         <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>18</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>31</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>26</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>10</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>37</v>
       </c>
     </row>
@@ -590,484 +623,592 @@
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>24</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>22</v>
       </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="n">
         <v>17</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CASTRO ESTRADA CINTHIA PATRICIA</t>
+          <t>CARRERA CARRASCO DEIVID FRANCISCO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>FABIANA REBECA ARRUNATEGUI SILUPU</t>
+          <t>CASTRO ESTRADA CINTHIA PATRICIA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>23</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" t="n">
         <v>14</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H6" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" t="n">
-        <v>19</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27</v>
-      </c>
-      <c r="L6" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>FLORES SILUPU MARY CARMEN</t>
+          <t>FABIANA REBECA ARRUNATEGUI SILUPU</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>29</v>
-      </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>19</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>27</v>
+      </c>
+      <c r="O7" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>GONZALES FIESTAS MARIA MARIBEL</t>
+          <t>FLORES SILUPU MARY CARMEN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13</v>
+      </c>
+      <c r="O8" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>HERNANDEZ CARNERO ARTURO SEBASTIAN</t>
+          <t>GONZALES FIESTAS MARIA MARIBEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>11</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>22</v>
-      </c>
-      <c r="I9" t="n">
-        <v>18</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>28</v>
+      </c>
+      <c r="L9" t="n">
+        <v>23</v>
+      </c>
+      <c r="M9" t="n">
+        <v>17</v>
+      </c>
+      <c r="N9" t="n">
         <v>19</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>24</v>
+      <c r="O9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>LLENQUE ANTON HELEN JOHANA</t>
+          <t>HERNANDEZ CARNERO ARTURO SEBASTIAN</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
         <v>22</v>
       </c>
-      <c r="C10" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" t="n">
-        <v>12</v>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="L10" t="n">
+        <v>18</v>
+      </c>
+      <c r="M10" t="n">
         <v>19</v>
       </c>
-      <c r="H10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>24</v>
-      </c>
-      <c r="I10" t="n">
-        <v>27</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" t="n">
-        <v>12</v>
-      </c>
-      <c r="L10" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MONDRAGON NONAJULCA MARISOL</t>
+          <t>LLENQUE ANTON HELEN JOHANA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19</v>
+      </c>
+      <c r="K11" t="n">
+        <v>24</v>
+      </c>
+      <c r="L11" t="n">
+        <v>27</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="n">
         <v>12</v>
       </c>
-      <c r="H11" t="n">
-        <v>22</v>
-      </c>
-      <c r="I11" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" t="n">
-        <v>15</v>
-      </c>
-      <c r="K11" t="n">
-        <v>13</v>
-      </c>
-      <c r="L11" t="n">
-        <v>17</v>
+      <c r="O11" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MORENO YANAYACO NAYLA GUADALUPE</t>
+          <t>MONDRAGON NONAJULCA MARISOL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>8</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N12" t="n">
         <v>13</v>
       </c>
-      <c r="I12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" t="n">
-        <v>12</v>
+      <c r="O12" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ORDINOLA JIBAJA JOSE ALBERTO</t>
+          <t>MORENO YANAYACO NAYLA GUADALUPE</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>23</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11</v>
+      </c>
+      <c r="O13" t="n">
         <v>12</v>
-      </c>
-      <c r="C13" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>15</v>
-      </c>
-      <c r="H13" t="n">
-        <v>20</v>
-      </c>
-      <c r="I13" t="n">
-        <v>13</v>
-      </c>
-      <c r="J13" t="n">
-        <v>13</v>
-      </c>
-      <c r="K13" t="n">
-        <v>15</v>
-      </c>
-      <c r="L13" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>PINTADO BENITES CRISTOBAL RODRIGO</t>
+          <t>ORDINOLA JIBAJA JOSE ALBERTO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>PINTADO CHASQUERO ESTEFANY</t>
+          <t>PINTADO BENITES CRISTOBAL RODRIGO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>RUIZ CHIROQUE CLAUDIA JUDITH</t>
+          <t>PINTADO CHASQUERO ESTEFANY</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1076,98 +1217,174 @@
         <v>10</v>
       </c>
       <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>19</v>
+      </c>
+      <c r="L16" t="n">
         <v>16</v>
       </c>
-      <c r="I16" t="n">
-        <v>23</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
+        <v>15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15</v>
+      </c>
+      <c r="O16" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>TEMOCHE ECHE URSULA YESSENIA</t>
+          <t>RUIZ CHIROQUE CLAUDIA JUDITH</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D17" t="n">
+        <v>19</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" t="n">
         <v>12</v>
       </c>
-      <c r="E17" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>24</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
+          <t>TEMOCHE ECHE URSULA YESSENIA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11</v>
+      </c>
+      <c r="K18" t="n">
+        <v>34</v>
+      </c>
+      <c r="L18" t="n">
+        <v>18</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18</v>
+      </c>
+      <c r="N18" t="n">
+        <v>14</v>
+      </c>
+      <c r="O18" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>VELASCO PEÑA KAREN ARELLYS</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>2</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>33</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>13</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>5</v>
       </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F19" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>13</v>
       </c>
-      <c r="H18" t="n">
+      <c r="K19" t="n">
         <v>22</v>
       </c>
-      <c r="I18" t="n">
+      <c r="L19" t="n">
         <v>20</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>29</v>
       </c>
-      <c r="L18" t="n">
+      <c r="O19" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1182,7 +1399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,30 +1435,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1269,33 +1501,44 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1323,29 +1566,44 @@
           <t>21</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -1377,29 +1635,40 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1408,593 +1677,682 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CASTRO ESTRADA CINTHIA PATRICIA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>CARRERA CARRASCO DEIVID FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>FABIANA REBECA ARRUNATEGUI SILUPU</t>
+          <t>CASTRO ESTRADA CINTHIA PATRICIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>FLORES SILUPU MARY CARMEN</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>FABIANA REBECA ARRUNATEGUI SILUPU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>GONZALES FIESTAS MARIA MARIBEL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>FLORES SILUPU MARY CARMEN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>HERNANDEZ CARNERO ARTURO SEBASTIAN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>GONZALES FIESTAS MARIA MARIBEL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>LLENQUE ANTON HELEN JOHANA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+          <t>HERNANDEZ CARNERO ARTURO SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MONDRAGON NONAJULCA MARISOL</t>
+          <t>LLENQUE ANTON HELEN JOHANA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>17</t>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MORENO YANAYACO NAYLA GUADALUPE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>MONDRAGON NONAJULCA MARISOL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ORDINOLA JIBAJA JOSE ALBERTO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>MORENO YANAYACO NAYLA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>PINTADO BENITES CRISTOBAL RODRIGO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>ORDINOLA JIBAJA JOSE ALBERTO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>PINTADO CHASQUERO ESTEFANY</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>PINTADO BENITES CRISTOBAL RODRIGO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>RUIZ CHIROQUE CLAUDIA JUDITH</t>
+          <t>PINTADO CHASQUERO ESTEFANY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -2005,21 +2363,40 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2028,114 +2405,197 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>TEMOCHE ECHE URSULA YESSENIA</t>
+          <t>RUIZ CHIROQUE CLAUDIA JUDITH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
+          <t>TEMOCHE ECHE URSULA YESSENIA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>VELASCO PEÑA KAREN ARELLYS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>17</t>
         </is>

--- a/data/la_villa_letira_becara.xlsx
+++ b/data/la_villa_letira_becara.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,30 +477,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -537,21 +547,27 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>19</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>27</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>20</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>12</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>16</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -583,24 +599,30 @@
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>18</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>31</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>26</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>37</v>
       </c>
     </row>
@@ -632,24 +654,30 @@
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>24</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>22</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>11</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>17</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -701,6 +729,12 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -733,21 +767,27 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>23</v>
-      </c>
-      <c r="L6" t="n">
-        <v>11</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>11</v>
       </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
         <v>14</v>
       </c>
     </row>
@@ -779,24 +819,30 @@
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>16</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>30</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>19</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>27</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>28</v>
       </c>
     </row>
@@ -828,24 +874,30 @@
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>29</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>13</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>39</v>
       </c>
     </row>
@@ -877,24 +929,30 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>11</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>28</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>23</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>17</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>19</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>26</v>
       </c>
     </row>
@@ -929,21 +987,27 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>12</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>22</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>18</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>19</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>24</v>
       </c>
     </row>
@@ -975,24 +1039,30 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>19</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>24</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>27</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>12</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1024,24 +1094,30 @@
         <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>12</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>22</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>14</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>13</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1073,24 +1149,30 @@
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>13</v>
-      </c>
-      <c r="L13" t="n">
-        <v>11</v>
-      </c>
-      <c r="M13" t="n">
-        <v>11</v>
       </c>
       <c r="N13" t="n">
         <v>11</v>
       </c>
       <c r="O13" t="n">
+        <v>11</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1122,24 +1204,30 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>15</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>20</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>13</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>13</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>15</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1180,15 +1268,21 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1223,21 +1317,27 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
+        <v>17</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>10</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>19</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>15</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>15</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1275,18 +1375,24 @@
         <v>10</v>
       </c>
       <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>23</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>24</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1321,21 +1427,27 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>11</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>34</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>18</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>18</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>14</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1367,24 +1479,30 @@
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>13</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>22</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>20</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>29</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1399,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,30 +1568,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1515,30 +1643,36 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1581,29 +1715,35 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -1646,29 +1786,35 @@
           <t>11</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1698,6 +1844,8 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1737,24 +1885,30 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1801,29 +1955,39 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -1868,27 +2032,33 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -1935,33 +2105,43 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2003,26 +2183,32 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -2069,33 +2255,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -2142,33 +2338,43 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -2207,33 +2413,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2276,33 +2492,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2324,14 +2550,16 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2373,30 +2601,36 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2447,21 +2681,31 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2507,30 +2751,36 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2573,29 +2823,39 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>17</t>
         </is>

--- a/data/la_villa_letira_becara.xlsx
+++ b/data/la_villa_letira_becara.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,30 +487,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -553,21 +558,24 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>19</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>27</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>20</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>12</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>16</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -605,24 +613,27 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>18</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>31</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>26</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>10</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>37</v>
       </c>
     </row>
@@ -660,24 +671,27 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>24</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>22</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>11</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>17</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -735,6 +749,9 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -776,18 +793,21 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>23</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>11</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>11</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>14</v>
       </c>
     </row>
@@ -825,24 +845,27 @@
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>16</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>30</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>19</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>27</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>28</v>
       </c>
     </row>
@@ -886,18 +909,21 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>29</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>20</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>13</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>39</v>
       </c>
     </row>
@@ -935,24 +961,27 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>11</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>28</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>23</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>17</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>19</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>26</v>
       </c>
     </row>
@@ -993,21 +1022,24 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>12</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>22</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>18</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>19</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1045,24 +1077,27 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>19</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>24</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>27</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>11</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>12</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1100,24 +1135,27 @@
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>12</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>22</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>14</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>15</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>13</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1155,16 +1193,16 @@
         <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>8</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>13</v>
-      </c>
-      <c r="N13" t="n">
-        <v>11</v>
       </c>
       <c r="O13" t="n">
         <v>11</v>
@@ -1173,6 +1211,9 @@
         <v>11</v>
       </c>
       <c r="Q13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1210,26 +1251,29 @@
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>15</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>20</v>
-      </c>
-      <c r="N14" t="n">
-        <v>13</v>
       </c>
       <c r="O14" t="n">
         <v>13</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
         <v>15</v>
       </c>
+      <c r="R14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1274,15 +1318,18 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1320,24 +1367,27 @@
         <v>17</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>10</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>19</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>16</v>
-      </c>
-      <c r="O16" t="n">
-        <v>15</v>
       </c>
       <c r="P16" t="n">
         <v>15</v>
       </c>
       <c r="Q16" t="n">
+        <v>15</v>
+      </c>
+      <c r="R16" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1378,21 +1428,24 @@
         <v>9</v>
       </c>
       <c r="L17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" t="n">
         <v>10</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>16</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>23</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>24</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1430,24 +1483,27 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>11</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>34</v>
-      </c>
-      <c r="N18" t="n">
-        <v>18</v>
       </c>
       <c r="O18" t="n">
         <v>18</v>
       </c>
       <c r="P18" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q18" t="n">
         <v>14</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1485,24 +1541,27 @@
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>13</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>22</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>20</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>29</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1517,7 +1576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1578,30 +1637,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1647,32 +1711,33 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1721,29 +1786,34 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -1792,29 +1862,34 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1846,6 +1921,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1892,23 +1968,24 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1965,29 +2042,34 @@
           <t>6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -2042,23 +2124,24 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -2115,33 +2198,38 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2187,28 +2275,29 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -2265,33 +2354,38 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -2348,33 +2442,38 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -2423,33 +2522,38 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2502,33 +2606,38 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2552,14 +2661,15 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2604,33 +2714,38 @@
           <t>17</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2686,26 +2801,31 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2754,33 +2874,38 @@
           <t>8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2833,29 +2958,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>17</t>
         </is>

--- a/data/la_villa_letira_becara.xlsx
+++ b/data/la_villa_letira_becara.xlsx
@@ -558,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>19</v>
@@ -616,7 +616,7 @@
         <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>18</v>
@@ -674,7 +674,7 @@
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>19</v>
@@ -1196,7 +1196,7 @@
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
         <v>8</v>
@@ -1486,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M18" t="n">
         <v>11</v>
@@ -1544,7 +1544,7 @@
         <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>13</v>
@@ -1711,7 +1711,11 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>19</t>
@@ -1791,7 +1795,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>18</t>
@@ -1867,7 +1875,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -1967,7 +1979,11 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
@@ -2123,7 +2139,11 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
@@ -2203,7 +2223,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>11</t>
@@ -2359,7 +2383,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>19</t>
@@ -2527,7 +2555,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>8</t>
@@ -2879,7 +2911,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2963,7 +2999,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>13</t>

--- a/data/la_villa_letira_becara.xlsx
+++ b/data/la_villa_letira_becara.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,30 +492,45 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -561,21 +576,30 @@
         <v>5</v>
       </c>
       <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>19</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>27</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>20</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>12</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>16</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -619,21 +643,30 @@
         <v>4</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>18</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>31</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>26</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>10</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>37</v>
       </c>
     </row>
@@ -647,7 +680,7 @@
         <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -680,18 +713,27 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>24</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>22</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>11</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>17</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -752,6 +794,15 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -796,18 +847,27 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>23</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>14</v>
       </c>
     </row>
@@ -851,21 +911,30 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>16</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>30</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>19</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>27</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>28</v>
       </c>
     </row>
@@ -912,18 +981,27 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>29</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>20</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>13</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>39</v>
       </c>
     </row>
@@ -967,21 +1045,30 @@
         <v>4</v>
       </c>
       <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>11</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>28</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>23</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>17</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>19</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1025,21 +1112,30 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
         <v>12</v>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>22</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>18</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>19</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1083,23 +1179,32 @@
         <v>2</v>
       </c>
       <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
         <v>19</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>24</v>
-      </c>
-      <c r="O11" t="n">
-        <v>27</v>
-      </c>
-      <c r="P11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>12</v>
       </c>
       <c r="R11" t="n">
         <v>27</v>
       </c>
+      <c r="S11" t="n">
+        <v>11</v>
+      </c>
+      <c r="T11" t="n">
+        <v>12</v>
+      </c>
+      <c r="U11" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1141,21 +1246,30 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
         <v>12</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>22</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>14</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>15</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>13</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1199,21 +1313,30 @@
         <v>5</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>8</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>13</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>11</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>11</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1257,21 +1380,30 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>15</v>
       </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
         <v>20</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>13</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>13</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>15</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1321,15 +1453,24 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1373,21 +1514,30 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>10</v>
       </c>
-      <c r="N16" t="n">
+      <c r="Q16" t="n">
         <v>19</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>16</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>15</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>15</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1431,21 +1581,30 @@
         <v>9</v>
       </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9</v>
+      </c>
+      <c r="P17" t="n">
         <v>10</v>
       </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
         <v>16</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>23</v>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>24</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1489,21 +1648,30 @@
         <v>9</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" t="n">
+      <c r="Q18" t="n">
         <v>34</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
         <v>18</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
         <v>18</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
         <v>14</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1547,21 +1715,30 @@
         <v>2</v>
       </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
         <v>13</v>
       </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
         <v>22</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
         <v>20</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>29</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1576,7 +1753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,30 +1819,45 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1718,30 +1910,37 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1800,28 +1999,31 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -1840,7 +2042,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1881,27 +2083,30 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1934,6 +2139,9 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1987,21 +2195,28 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2064,28 +2279,35 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -2145,23 +2367,30 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -2230,30 +2459,37 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2302,26 +2538,37 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -2390,30 +2637,41 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -2478,30 +2736,41 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -2560,32 +2829,35 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2644,32 +2916,35 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2694,14 +2969,17 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2754,30 +3032,41 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2836,28 +3125,39 @@
           <t>9</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2916,32 +3216,35 @@
           <t>9</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -3004,28 +3307,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>17</t>
         </is>

--- a/data/la_villa_letira_becara.xlsx
+++ b/data/la_villa_letira_becara.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,30 +507,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -585,21 +590,24 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>19</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>27</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>20</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>12</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>16</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -652,21 +660,24 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>18</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>31</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>10</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>37</v>
       </c>
     </row>
@@ -722,18 +733,21 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>24</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>22</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>11</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>17</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -803,6 +817,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -856,18 +873,21 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>23</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>11</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>14</v>
       </c>
     </row>
@@ -920,21 +940,24 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>16</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>30</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>19</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>27</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>28</v>
       </c>
     </row>
@@ -990,18 +1013,21 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>29</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>20</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>13</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1054,21 +1080,24 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>11</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>28</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>23</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>17</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>19</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1121,21 +1150,24 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>12</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>22</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>18</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>19</v>
       </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1188,21 +1220,24 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>19</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>24</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>27</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>11</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>12</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1255,21 +1290,24 @@
         <v>8</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>12</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>22</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>14</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>15</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>13</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1322,13 +1360,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>8</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>13</v>
-      </c>
-      <c r="R13" t="n">
-        <v>11</v>
       </c>
       <c r="S13" t="n">
         <v>11</v>
@@ -1337,6 +1375,9 @@
         <v>11</v>
       </c>
       <c r="U13" t="n">
+        <v>11</v>
+      </c>
+      <c r="V13" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1389,23 +1430,26 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>15</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>20</v>
-      </c>
-      <c r="R14" t="n">
-        <v>13</v>
       </c>
       <c r="S14" t="n">
         <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U14" t="n">
         <v>15</v>
       </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1462,15 +1506,18 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1523,21 +1570,24 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>10</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>19</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>16</v>
-      </c>
-      <c r="S16" t="n">
-        <v>15</v>
       </c>
       <c r="T16" t="n">
         <v>15</v>
       </c>
       <c r="U16" t="n">
+        <v>15</v>
+      </c>
+      <c r="V16" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1590,21 +1640,24 @@
         <v>9</v>
       </c>
       <c r="P17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>16</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>23</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>24</v>
       </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1657,21 +1710,24 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>11</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>34</v>
-      </c>
-      <c r="R18" t="n">
-        <v>18</v>
       </c>
       <c r="S18" t="n">
         <v>18</v>
       </c>
       <c r="T18" t="n">
+        <v>18</v>
+      </c>
+      <c r="U18" t="n">
         <v>14</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1724,21 +1780,24 @@
         <v>3</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>13</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>22</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>20</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>29</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1753,7 +1812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1834,30 +1893,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1915,32 +1979,33 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2002,28 +2067,29 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -2086,27 +2152,28 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -2142,6 +2209,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2200,23 +2268,24 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2286,28 +2355,29 @@
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -2374,23 +2444,24 @@
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -2464,32 +2535,33 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2547,28 +2619,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -2646,32 +2719,33 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -2745,32 +2819,33 @@
           <t>8</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -2832,32 +2907,33 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2919,32 +2995,33 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2972,14 +3049,15 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3043,30 +3121,35 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -3138,26 +3221,31 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -3219,32 +3307,33 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -3314,28 +3403,29 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>17</t>
         </is>
